--- a/site/exportExcel/word2Vec.xlsx
+++ b/site/exportExcel/word2Vec.xlsx
@@ -456,16 +456,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.3294857740402222</v>
+        <v>0.5476183891296387</v>
       </c>
     </row>
     <row r="3">
@@ -474,16 +474,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.3203414380550385</v>
+        <v>-0.2219346016645432</v>
       </c>
     </row>
     <row r="4">
@@ -492,16 +492,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3009065687656403</v>
+        <v>0.3022493720054626</v>
       </c>
     </row>
     <row r="5">
@@ -510,16 +510,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.1053181141614914</v>
+        <v>0.1095166727900505</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4723374843597412</v>
+        <v>-0.2348822355270386</v>
       </c>
     </row>
     <row r="7">
@@ -546,16 +546,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3476644158363342</v>
+        <v>0.3802090287208557</v>
       </c>
     </row>
     <row r="8">
@@ -564,16 +564,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4699983298778534</v>
+        <v>-0.5152461528778076</v>
       </c>
     </row>
     <row r="9">
@@ -582,16 +582,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.08754055202007294</v>
+        <v>0.1743868738412857</v>
       </c>
     </row>
     <row r="10">
@@ -600,16 +600,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.06197946891188622</v>
+        <v>-0.187346875667572</v>
       </c>
     </row>
     <row r="11">
@@ -618,16 +618,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3294857740402222</v>
+        <v>0.5476183891296387</v>
       </c>
     </row>
     <row r="12">
@@ -636,16 +636,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.5384165644645691</v>
+        <v>-0.5397290587425232</v>
       </c>
     </row>
     <row r="13">
@@ -654,16 +654,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.5437305569648743</v>
+        <v>0.3341339528560638</v>
       </c>
     </row>
     <row r="14">
@@ -672,16 +672,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.2111628651618958</v>
+        <v>-0.2033715397119522</v>
       </c>
     </row>
     <row r="15">
@@ -690,16 +690,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.0287444144487381</v>
+        <v>-0.3213414251804352</v>
       </c>
     </row>
     <row r="16">
@@ -708,16 +708,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.003877876326441765</v>
+        <v>0.03760277479887009</v>
       </c>
     </row>
     <row r="17">
@@ -726,16 +726,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.03390561044216156</v>
+        <v>-0.634380042552948</v>
       </c>
     </row>
     <row r="18">
@@ -744,16 +744,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.180061548948288</v>
+        <v>-0.03604961559176445</v>
       </c>
     </row>
     <row r="19">
@@ -762,16 +762,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.3210886418819427</v>
+        <v>-0.1783687174320221</v>
       </c>
     </row>
     <row r="20">
@@ -780,16 +780,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.3203414380550385</v>
+        <v>-0.2219346016645432</v>
       </c>
     </row>
     <row r="21">
@@ -798,16 +798,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.5384165644645691</v>
+        <v>-0.5397290587425232</v>
       </c>
     </row>
     <row r="22">
@@ -816,16 +816,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.2246029078960419</v>
+        <v>-0.3192259073257446</v>
       </c>
     </row>
     <row r="23">
@@ -834,16 +834,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.3665652871131897</v>
+        <v>-0.3645497858524323</v>
       </c>
     </row>
     <row r="24">
@@ -852,16 +852,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.3632927536964417</v>
+        <v>0.1094977408647537</v>
       </c>
     </row>
     <row r="25">
@@ -870,16 +870,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.3559308052062988</v>
+        <v>-0.3016672134399414</v>
       </c>
     </row>
     <row r="26">
@@ -888,16 +888,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.02677037939429283</v>
+        <v>0.3414679169654846</v>
       </c>
     </row>
     <row r="27">
@@ -906,16 +906,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.6142536997795105</v>
+        <v>-0.1606930792331696</v>
       </c>
     </row>
     <row r="28">
@@ -924,16 +924,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.1119248196482658</v>
+        <v>0.6148960590362549</v>
       </c>
     </row>
     <row r="29">
@@ -942,16 +942,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.3009065687656403</v>
+        <v>0.3022493720054626</v>
       </c>
     </row>
     <row r="30">
@@ -960,16 +960,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5437305569648743</v>
+        <v>0.3341339528560638</v>
       </c>
     </row>
     <row r="31">
@@ -978,16 +978,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-0.2246029078960419</v>
+        <v>-0.3192259073257446</v>
       </c>
     </row>
     <row r="32">
@@ -996,16 +996,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.1049270480871201</v>
+        <v>-0.1018027514219284</v>
       </c>
     </row>
     <row r="33">
@@ -1014,16 +1014,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-0.182675376534462</v>
+        <v>-0.06162996962666512</v>
       </c>
     </row>
     <row r="34">
@@ -1032,16 +1032,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-0.09684580564498901</v>
+        <v>-0.1118969023227692</v>
       </c>
     </row>
     <row r="35">
@@ -1050,16 +1050,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.4318859577178955</v>
+        <v>-0.618388295173645</v>
       </c>
     </row>
     <row r="36">
@@ -1068,16 +1068,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-0.1901353001594543</v>
+        <v>-0.1486065983772278</v>
       </c>
     </row>
     <row r="37">
@@ -1086,16 +1086,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-0.2368525266647339</v>
+        <v>-0.08747614175081253</v>
       </c>
     </row>
     <row r="38">
@@ -1104,16 +1104,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-0.1053181141614914</v>
+        <v>0.1095166727900505</v>
       </c>
     </row>
     <row r="39">
@@ -1122,16 +1122,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-0.2111628651618958</v>
+        <v>-0.2033715397119522</v>
       </c>
     </row>
     <row r="40">
@@ -1140,16 +1140,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-0.3665652871131897</v>
+        <v>-0.3645497858524323</v>
       </c>
     </row>
     <row r="41">
@@ -1158,16 +1158,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.1049270480871201</v>
+        <v>-0.1018027514219284</v>
       </c>
     </row>
     <row r="42">
@@ -1176,16 +1176,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.1618327349424362</v>
+        <v>-0.1906304955482483</v>
       </c>
     </row>
     <row r="43">
@@ -1194,16 +1194,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.3088885545730591</v>
+        <v>0.2078994512557983</v>
       </c>
     </row>
     <row r="44">
@@ -1212,16 +1212,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.199435293674469</v>
+        <v>0.2906926274299622</v>
       </c>
     </row>
     <row r="45">
@@ -1230,16 +1230,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-0.1137513816356659</v>
+        <v>0.09569701552391052</v>
       </c>
     </row>
     <row r="46">
@@ -1248,16 +1248,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-0.1919147223234177</v>
+        <v>-0.111284427344799</v>
       </c>
     </row>
     <row r="47">
@@ -1266,16 +1266,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.4723374843597412</v>
+        <v>-0.2348822355270386</v>
       </c>
     </row>
     <row r="48">
@@ -1284,16 +1284,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-0.0287444144487381</v>
+        <v>-0.3213414251804352</v>
       </c>
     </row>
     <row r="49">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-0.3632927536964417</v>
+        <v>0.1094977408647537</v>
       </c>
     </row>
     <row r="50">
@@ -1320,16 +1320,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-0.182675376534462</v>
+        <v>-0.06162996962666512</v>
       </c>
     </row>
     <row r="51">
@@ -1338,16 +1338,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.1618327349424362</v>
+        <v>-0.1906304955482483</v>
       </c>
     </row>
     <row r="52">
@@ -1356,16 +1356,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.1264803111553192</v>
+        <v>-0.1072554141283035</v>
       </c>
     </row>
     <row r="53">
@@ -1374,16 +1374,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-0.1144016906619072</v>
+        <v>0.2800647020339966</v>
       </c>
     </row>
     <row r="54">
@@ -1392,16 +1392,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.004038990009576082</v>
+        <v>-0.3024807572364807</v>
       </c>
     </row>
     <row r="55">
@@ -1410,16 +1410,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.3292985856533051</v>
+        <v>0.220086082816124</v>
       </c>
     </row>
     <row r="56">
@@ -1428,16 +1428,16 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.3476644158363342</v>
+        <v>0.3802090287208557</v>
       </c>
     </row>
     <row r="57">
@@ -1446,16 +1446,16 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.003877876326441765</v>
+        <v>0.03760277479887009</v>
       </c>
     </row>
     <row r="58">
@@ -1464,16 +1464,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-0.3559308052062988</v>
+        <v>-0.3016672134399414</v>
       </c>
     </row>
     <row r="59">
@@ -1482,16 +1482,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-0.09684580564498901</v>
+        <v>-0.1118969023227692</v>
       </c>
     </row>
     <row r="60">
@@ -1500,16 +1500,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.3088885545730591</v>
+        <v>0.2078994512557983</v>
       </c>
     </row>
     <row r="61">
@@ -1518,16 +1518,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.1264803111553192</v>
+        <v>-0.1072554141283035</v>
       </c>
     </row>
     <row r="62">
@@ -1536,16 +1536,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.05181539058685303</v>
+        <v>0.141809493303299</v>
       </c>
     </row>
     <row r="63">
@@ -1554,16 +1554,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-0.3427785336971283</v>
+        <v>-0.0970262810587883</v>
       </c>
     </row>
     <row r="64">
@@ -1572,16 +1572,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-0.409724622964859</v>
+        <v>-0.3894533216953278</v>
       </c>
     </row>
     <row r="65">
@@ -1590,16 +1590,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.4699983298778534</v>
+        <v>-0.5152461528778076</v>
       </c>
     </row>
     <row r="66">
@@ -1608,16 +1608,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.03390561044216156</v>
+        <v>-0.634380042552948</v>
       </c>
     </row>
     <row r="67">
@@ -1626,16 +1626,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.02677037939429283</v>
+        <v>0.3414679169654846</v>
       </c>
     </row>
     <row r="68">
@@ -1644,16 +1644,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.4318859577178955</v>
+        <v>-0.618388295173645</v>
       </c>
     </row>
     <row r="69">
@@ -1662,16 +1662,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.199435293674469</v>
+        <v>0.2906926274299622</v>
       </c>
     </row>
     <row r="70">
@@ -1680,16 +1680,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.1144016906619072</v>
+        <v>0.2800647020339966</v>
       </c>
     </row>
     <row r="71">
@@ -1698,16 +1698,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.05181539058685303</v>
+        <v>0.141809493303299</v>
       </c>
     </row>
     <row r="72">
@@ -1716,16 +1716,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-0.2463994473218918</v>
+        <v>-0.3615615963935852</v>
       </c>
     </row>
     <row r="73">
@@ -1734,16 +1734,16 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-0.440651148557663</v>
+        <v>0.1666093170642853</v>
       </c>
     </row>
     <row r="74">
@@ -1752,16 +1752,16 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>-0.08754055202007294</v>
+        <v>0.1743868738412857</v>
       </c>
     </row>
     <row r="75">
@@ -1770,16 +1770,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>-0.180061548948288</v>
+        <v>-0.03604961559176445</v>
       </c>
     </row>
     <row r="76">
@@ -1788,16 +1788,16 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.6142536997795105</v>
+        <v>-0.1606930792331696</v>
       </c>
     </row>
     <row r="77">
@@ -1806,16 +1806,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-0.1901353001594543</v>
+        <v>-0.1486065983772278</v>
       </c>
     </row>
     <row r="78">
@@ -1824,16 +1824,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-0.1137513816356659</v>
+        <v>0.09569701552391052</v>
       </c>
     </row>
     <row r="79">
@@ -1842,16 +1842,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.004038990009576082</v>
+        <v>-0.3024807572364807</v>
       </c>
     </row>
     <row r="80">
@@ -1860,16 +1860,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-0.3427785336971283</v>
+        <v>-0.0970262810587883</v>
       </c>
     </row>
     <row r="81">
@@ -1878,16 +1878,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-0.2463994473218918</v>
+        <v>-0.3615615963935852</v>
       </c>
     </row>
     <row r="82">
@@ -1896,16 +1896,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.220897912979126</v>
+        <v>-0.5749166011810303</v>
       </c>
     </row>
     <row r="83">
@@ -1914,16 +1914,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>to</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>-0.06197946891188622</v>
+        <v>-0.187346875667572</v>
       </c>
     </row>
     <row r="84">
@@ -1932,16 +1932,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>get</t>
+          <t>,</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-0.3210886418819427</v>
+        <v>-0.1783687174320221</v>
       </c>
     </row>
     <row r="85">
@@ -1950,16 +1950,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>.</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.1119248196482658</v>
+        <v>0.6148960590362549</v>
       </c>
     </row>
     <row r="86">
@@ -1968,16 +1968,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>the</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-0.2368525266647339</v>
+        <v>-0.08747614175081253</v>
       </c>
     </row>
     <row r="87">
@@ -1986,16 +1986,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>say</t>
+          <t>a</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-0.1919147223234177</v>
+        <v>-0.111284427344799</v>
       </c>
     </row>
     <row r="88">
@@ -2004,16 +2004,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>lose</t>
+          <t>but</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.3292985856533051</v>
+        <v>0.220086082816124</v>
       </c>
     </row>
     <row r="89">
@@ -2022,16 +2022,16 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-0.409724622964859</v>
+        <v>-0.3894533216953278</v>
       </c>
     </row>
     <row r="90">
@@ -2040,16 +2040,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>that</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-0.440651148557663</v>
+        <v>0.1666093170642853</v>
       </c>
     </row>
     <row r="91">
@@ -2058,16 +2058,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>[</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>vip</t>
+          <t>its</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.220897912979126</v>
+        <v>-0.5749166011810303</v>
       </c>
     </row>
   </sheetData>
